--- a/src/OngGio.Infrastructure/Templates/BaoGiaExportTemplate.xlsx
+++ b/src/OngGio.Infrastructure/Templates/BaoGiaExportTemplate.xlsx
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -247,6 +247,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -759,7 +762,7 @@
       <c r="I5" s="11" t="n"/>
       <c r="J5" s="11" t="n"/>
       <c r="K5" s="11" t="n"/>
-      <c r="L5" s="13" t="n"/>
+      <c r="L5" s="22" t="n"/>
       <c r="M5" s="14" t="n"/>
       <c r="N5" s="14" t="n"/>
       <c r="O5" s="15" t="n"/>

--- a/src/OngGio.Infrastructure/Templates/BaoGiaExportTemplate.xlsx
+++ b/src/OngGio.Infrastructure/Templates/BaoGiaExportTemplate.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project_Ong_gio\src\OngGio.Infrastructure\Templates\"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>BẢNG TÍNH GIÁ ỐNG GIÓ</t>
   </si>
@@ -93,6 +93,48 @@
   </si>
   <si>
     <t xml:space="preserve">2/ Có 4 loại độ dày tôn thông dụng : 0.58mm, 0.75mm, 0.95mm và 1.15 mm ( tùy vào yêu cầu của khách hàng ) </t>
+  </si>
+  <si>
+    <t>CÔNG TY TNHH SX TM DV CƠ ĐIỆN THUẬN PHONG</t>
+  </si>
+  <si>
+    <t>PHÒNG DỰ ÁN</t>
+  </si>
+  <si>
+    <t>Đc: 223 Trường Chinh, P .An Khê, Tp. Đà Nẵng</t>
+  </si>
+  <si>
+    <t>Mail: sales@codienthuanphong.com.vn</t>
+  </si>
+  <si>
+    <t>BÁO GIÁ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kính gửi: </t>
+  </si>
+  <si>
+    <t>Đơn vị:    THUẬN PHONG M&amp;E CO.Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Địa chỉ: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Người nhận: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Người gửi: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mail: </t>
+  </si>
+  <si>
+    <t>Mail:  kythuat2@codienthuanphong.com.vn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellphone: </t>
+  </si>
+  <si>
+    <t>Cellphone: 0935 610 595</t>
   </si>
 </sst>
 </file>
@@ -103,7 +145,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,6 +216,37 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -257,69 +330,84 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -336,6 +424,44 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1524000" cy="857250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="company-logo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1524000" cy="857250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -623,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A2:O24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" customWidth="1"/>
@@ -634,188 +760,321 @@
     <col min="6" max="6" width="19.42578125" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
     <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
     <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" customWidth="1"/>
     <col min="13" max="13" width="19" customWidth="1"/>
     <col min="14" max="14" width="19.42578125" customWidth="1"/>
     <col min="15" max="15" width="49" customWidth="1"/>
     <col min="16" max="16" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O2" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O3" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O4" s="18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O6" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+    </row>
+    <row r="9" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="G9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+    </row>
+    <row r="10" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="G11" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+    </row>
+    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="G12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+    </row>
+    <row r="13" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="G13" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+    </row>
+    <row r="14" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-    </row>
-    <row r="2" spans="1:15" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-    </row>
-    <row r="3" spans="1:15" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+    </row>
+    <row r="15" spans="1:15" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+    </row>
+    <row r="16" spans="1:15" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B16" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C16" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D16" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E16" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F16" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G16" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I16" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="21" t="s">
+      <c r="M16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="N16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="O16" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-    </row>
-    <row r="5" spans="1:15" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="22"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+    <row r="17" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+    </row>
+    <row r="18" spans="1:15" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="25"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B19" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="14" t="s">
+      <c r="C19" s="26"/>
+      <c r="D19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="13"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C8" s="9"/>
-      <c r="D8" s="14" t="s">
+      <c r="E19" s="9"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C21" s="27"/>
+      <c r="D21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="13"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
+      <c r="E21" s="9"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B23" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B24" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="B3:B4"/>
+  <mergeCells count="29">
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="G12:O12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="G13:O13"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="G9:O9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="G11:O11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/OngGio.Infrastructure/Templates/BaoGiaExportTemplate.xlsx
+++ b/src/OngGio.Infrastructure/Templates/BaoGiaExportTemplate.xlsx
@@ -110,21 +110,12 @@
     <t>BÁO GIÁ</t>
   </si>
   <si>
-    <t xml:space="preserve">Kính gửi: </t>
-  </si>
-  <si>
     <t>Đơn vị:    THUẬN PHONG M&amp;E CO.Ltd</t>
   </si>
   <si>
-    <t xml:space="preserve">Địa chỉ: </t>
-  </si>
-  <si>
     <t xml:space="preserve">Người nhận: </t>
   </si>
   <si>
-    <t xml:space="preserve">Người gửi: </t>
-  </si>
-  <si>
     <t xml:space="preserve">Mail: </t>
   </si>
   <si>
@@ -135,6 +126,15 @@
   </si>
   <si>
     <t>Cellphone: 0935 610 595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Người gửi:…. </t>
+  </si>
+  <si>
+    <t>Kính gửi: ….</t>
+  </si>
+  <si>
+    <t>Địa chỉ: ….</t>
   </si>
 </sst>
 </file>
@@ -145,7 +145,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,21 +219,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="20"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -242,7 +227,29 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -330,84 +337,86 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -431,11 +440,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>408213</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>122463</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1524000" cy="857250"/>
+    <xdr:ext cx="2558143" cy="1438956"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="company-logo"/>
@@ -451,8 +460,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="1524000" cy="857250"/>
+          <a:off x="408213" y="122463"/>
+          <a:ext cx="2558143" cy="1438956"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -760,7 +769,7 @@
     <col min="6" max="6" width="19.42578125" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
     <col min="8" max="8" width="16.42578125" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" customWidth="1"/>
     <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
     <col min="12" max="12" width="9.140625" customWidth="1"/>
@@ -771,276 +780,301 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O2" s="17" t="s">
+      <c r="O2" s="13" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O4" s="18" t="s">
+      <c r="O4" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O5" s="15"/>
+    </row>
     <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O6" s="17" t="s">
+      <c r="O6" s="13" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-    </row>
-    <row r="9" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+    </row>
+    <row r="9" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="G9" s="11" t="s">
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+    </row>
+    <row r="10" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+    </row>
+    <row r="11" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-    </row>
-    <row r="10" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+    </row>
+    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-    </row>
-    <row r="11" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="B12" s="18"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="G11" s="11" t="s">
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+    </row>
+    <row r="13" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-    </row>
-    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="B13" s="18"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="G12" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-    </row>
-    <row r="13" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="G13" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
     </row>
     <row r="14" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
     </row>
     <row r="15" spans="1:15" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
     </row>
     <row r="16" spans="1:15" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="M16" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="N16" s="3" t="s">
+      <c r="N16" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="O16" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
     </row>
     <row r="18" spans="1:15" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="25"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="10"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="1" t="s">
+      <c r="C19" s="11"/>
+      <c r="D19" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="9"/>
+      <c r="E19" s="24"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C21" s="27"/>
-      <c r="D21" s="1" t="s">
+      <c r="C21" s="12"/>
+      <c r="D21" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="9"/>
+      <c r="E21" s="24"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -1075,6 +1109,7 @@
     <mergeCell ref="G11:O11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>